--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/Panel-28/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -470,28 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.99363</v>
+        <v>16.9614</v>
       </c>
       <c r="D2" t="n">
-        <v>16.59944</v>
+        <v>16.45546</v>
       </c>
       <c r="E2" t="n">
-        <v>16.79587</v>
+        <v>16.50223</v>
       </c>
       <c r="F2" t="n">
-        <v>54.53569</v>
+        <v>42.33717</v>
       </c>
       <c r="G2" t="n">
-        <v>41.7892</v>
+        <v>0.05032</v>
       </c>
       <c r="H2" t="n">
-        <v>85.44548</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.05099</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.82192</v>
+        <v>1.78366</v>
       </c>
     </row>
     <row r="3">
@@ -501,28 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.52997</v>
+        <v>16.96084</v>
       </c>
       <c r="D3" t="n">
-        <v>16.51413</v>
+        <v>16.69025</v>
       </c>
       <c r="E3" t="n">
-        <v>16.486</v>
+        <v>16.82762</v>
       </c>
       <c r="F3" t="n">
-        <v>54.17712</v>
+        <v>42.53861</v>
       </c>
       <c r="G3" t="n">
-        <v>42.09191</v>
+        <v>0.05029</v>
       </c>
       <c r="H3" t="n">
-        <v>83.92592999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.05068</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.81668</v>
+        <v>1.84152</v>
       </c>
     </row>
     <row r="4">
@@ -532,28 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.80952</v>
+        <v>16.78155</v>
       </c>
       <c r="D4" t="n">
-        <v>16.66541</v>
+        <v>16.52133</v>
       </c>
       <c r="E4" t="n">
-        <v>16.35372</v>
+        <v>16.53055</v>
       </c>
       <c r="F4" t="n">
-        <v>55.28146</v>
+        <v>42.7518</v>
       </c>
       <c r="G4" t="n">
-        <v>41.92456</v>
+        <v>0.05083</v>
       </c>
       <c r="H4" t="n">
-        <v>85.45862</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.05066</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.79705</v>
+        <v>1.79088</v>
       </c>
     </row>
     <row r="5">
@@ -563,28 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.79075</v>
+        <v>16.60164</v>
       </c>
       <c r="D5" t="n">
-        <v>16.51713</v>
+        <v>16.50032</v>
       </c>
       <c r="E5" t="n">
-        <v>16.73568</v>
+        <v>16.58971</v>
       </c>
       <c r="F5" t="n">
-        <v>55.51239</v>
+        <v>42.72797</v>
       </c>
       <c r="G5" t="n">
-        <v>42.1844</v>
+        <v>0.04976</v>
       </c>
       <c r="H5" t="n">
-        <v>84.01315</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.04937</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.81338</v>
+        <v>1.82377</v>
       </c>
     </row>
     <row r="6">
@@ -594,28 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.8229</v>
+        <v>16.58169</v>
       </c>
       <c r="D6" t="n">
-        <v>16.30052</v>
+        <v>16.20303</v>
       </c>
       <c r="E6" t="n">
-        <v>16.44844</v>
+        <v>16.52634</v>
       </c>
       <c r="F6" t="n">
-        <v>55.5381</v>
+        <v>43.04664</v>
       </c>
       <c r="G6" t="n">
-        <v>42.08741</v>
+        <v>0.05</v>
       </c>
       <c r="H6" t="n">
-        <v>83.69177000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.05087</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.83535</v>
+        <v>1.79312</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.90209</v>
+        <v>16.67254</v>
       </c>
       <c r="D7" t="n">
-        <v>16.52803</v>
+        <v>16.39802</v>
       </c>
       <c r="E7" t="n">
-        <v>16.41373</v>
+        <v>16.64644</v>
       </c>
       <c r="F7" t="n">
-        <v>54.33453</v>
+        <v>41.89028</v>
       </c>
       <c r="G7" t="n">
-        <v>42.60186</v>
+        <v>0.05054</v>
       </c>
       <c r="H7" t="n">
-        <v>85.2495</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.05007</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.79556</v>
+        <v>1.81853</v>
       </c>
     </row>
     <row r="8">
@@ -656,28 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.09445</v>
+        <v>16.93661</v>
       </c>
       <c r="D8" t="n">
-        <v>16.14186</v>
+        <v>16.23601</v>
       </c>
       <c r="E8" t="n">
-        <v>16.68027</v>
+        <v>16.44683</v>
       </c>
       <c r="F8" t="n">
-        <v>54.92443</v>
+        <v>43.23754</v>
       </c>
       <c r="G8" t="n">
-        <v>42.67528</v>
+        <v>0.05092</v>
       </c>
       <c r="H8" t="n">
-        <v>84.70968000000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.05118</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.83207</v>
+        <v>1.80894</v>
       </c>
     </row>
     <row r="9">
@@ -687,28 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.52863</v>
+        <v>17.00563</v>
       </c>
       <c r="D9" t="n">
-        <v>16.096</v>
+        <v>16.40488</v>
       </c>
       <c r="E9" t="n">
-        <v>16.64154</v>
+        <v>16.72239</v>
       </c>
       <c r="F9" t="n">
-        <v>57.03927</v>
+        <v>42.99994</v>
       </c>
       <c r="G9" t="n">
-        <v>41.88859</v>
+        <v>0.05046</v>
       </c>
       <c r="H9" t="n">
-        <v>84.14688</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.04926</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.82482</v>
+        <v>1.82231</v>
       </c>
     </row>
     <row r="10">
@@ -718,28 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.67477</v>
+        <v>16.72581</v>
       </c>
       <c r="D10" t="n">
-        <v>16.49198</v>
+        <v>16.54057</v>
       </c>
       <c r="E10" t="n">
-        <v>16.81378</v>
+        <v>16.70172</v>
       </c>
       <c r="F10" t="n">
-        <v>54.28085</v>
+        <v>41.46141</v>
       </c>
       <c r="G10" t="n">
-        <v>42.17005</v>
+        <v>0.05033</v>
       </c>
       <c r="H10" t="n">
-        <v>83.95877</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.04909</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.8202</v>
+        <v>1.7907</v>
       </c>
     </row>
     <row r="11">
@@ -760,25 +696,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -796,28 +722,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.04205</v>
+        <v>16.84943</v>
       </c>
       <c r="D12" t="n">
-        <v>16.69626</v>
+        <v>16.50303</v>
       </c>
       <c r="E12" t="n">
-        <v>16.50503</v>
+        <v>16.59409</v>
       </c>
       <c r="F12" t="n">
-        <v>55.48968</v>
+        <v>41.92024</v>
       </c>
       <c r="G12" t="n">
-        <v>42.26097</v>
+        <v>0.04934</v>
       </c>
       <c r="H12" t="n">
-        <v>82.99386</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.04967</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.77215</v>
+        <v>1.83098</v>
       </c>
     </row>
     <row r="13">
@@ -827,28 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.91929</v>
+        <v>16.54749</v>
       </c>
       <c r="D13" t="n">
-        <v>16.44401</v>
+        <v>16.25517</v>
       </c>
       <c r="E13" t="n">
-        <v>16.63495</v>
+        <v>16.43167</v>
       </c>
       <c r="F13" t="n">
-        <v>54.86619</v>
+        <v>41.52428</v>
       </c>
       <c r="G13" t="n">
-        <v>41.9738</v>
+        <v>0.0505</v>
       </c>
       <c r="H13" t="n">
-        <v>83.99279</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.05064</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.81397</v>
+        <v>1.8048</v>
       </c>
     </row>
     <row r="14">
@@ -858,28 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.6022</v>
+        <v>16.68839</v>
       </c>
       <c r="D14" t="n">
-        <v>16.4361</v>
+        <v>16.44641</v>
       </c>
       <c r="E14" t="n">
-        <v>16.64416</v>
+        <v>16.68265</v>
       </c>
       <c r="F14" t="n">
-        <v>56.6135</v>
+        <v>41.89135</v>
       </c>
       <c r="G14" t="n">
-        <v>42.45422</v>
+        <v>0.05095</v>
       </c>
       <c r="H14" t="n">
-        <v>83.06157</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.04967</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.79378</v>
+        <v>1.83737</v>
       </c>
     </row>
     <row r="15">
@@ -889,28 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.45854</v>
+        <v>16.97668</v>
       </c>
       <c r="D15" t="n">
-        <v>16.38654</v>
+        <v>16.31697</v>
       </c>
       <c r="E15" t="n">
-        <v>16.59132</v>
+        <v>16.66714</v>
       </c>
       <c r="F15" t="n">
-        <v>54.73054</v>
+        <v>42.70883</v>
       </c>
       <c r="G15" t="n">
-        <v>42.59447</v>
+        <v>0.04902</v>
       </c>
       <c r="H15" t="n">
-        <v>85.8677</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.04987</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.83381</v>
+        <v>1.78995</v>
       </c>
     </row>
     <row r="16">
@@ -920,28 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.71434</v>
+        <v>16.80567</v>
       </c>
       <c r="D16" t="n">
-        <v>16.48258</v>
+        <v>16.22304</v>
       </c>
       <c r="E16" t="n">
-        <v>16.67303</v>
+        <v>16.7499</v>
       </c>
       <c r="F16" t="n">
-        <v>55.75806</v>
+        <v>43.12926</v>
       </c>
       <c r="G16" t="n">
-        <v>42.39406</v>
+        <v>0.05071</v>
       </c>
       <c r="H16" t="n">
-        <v>82.02106999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.04965</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.80863</v>
+        <v>1.81364</v>
       </c>
     </row>
     <row r="17">
@@ -951,28 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.64543</v>
+        <v>16.90281</v>
       </c>
       <c r="D17" t="n">
-        <v>16.56328</v>
+        <v>16.38914</v>
       </c>
       <c r="E17" t="n">
-        <v>16.6104</v>
+        <v>16.76943</v>
       </c>
       <c r="F17" t="n">
-        <v>54.55474</v>
+        <v>42.45931</v>
       </c>
       <c r="G17" t="n">
-        <v>42.04991</v>
+        <v>0.05115</v>
       </c>
       <c r="H17" t="n">
-        <v>84.91970999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.05125</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.80378</v>
+        <v>1.81246</v>
       </c>
     </row>
     <row r="18">
@@ -982,28 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.5705</v>
+        <v>16.87048</v>
       </c>
       <c r="D18" t="n">
-        <v>16.32023</v>
+        <v>16.53923</v>
       </c>
       <c r="E18" t="n">
-        <v>16.65363</v>
+        <v>16.69709</v>
       </c>
       <c r="F18" t="n">
-        <v>54.95461</v>
+        <v>41.36801</v>
       </c>
       <c r="G18" t="n">
-        <v>42.7126</v>
+        <v>0.04982</v>
       </c>
       <c r="H18" t="n">
-        <v>83.95939</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.05004</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.80731</v>
+        <v>1.80179</v>
       </c>
     </row>
     <row r="19">
@@ -1013,28 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.72079</v>
+        <v>17.08227</v>
       </c>
       <c r="D19" t="n">
-        <v>16.46114</v>
+        <v>16.78531</v>
       </c>
       <c r="E19" t="n">
-        <v>16.25745</v>
+        <v>16.80701</v>
       </c>
       <c r="F19" t="n">
-        <v>53.33187</v>
+        <v>42.45147</v>
       </c>
       <c r="G19" t="n">
-        <v>41.63132</v>
+        <v>0.04965</v>
       </c>
       <c r="H19" t="n">
-        <v>85.94325000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.04917</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.78899</v>
+        <v>1.78182</v>
       </c>
     </row>
     <row r="20">
@@ -1044,28 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.59776</v>
+        <v>16.94014</v>
       </c>
       <c r="D20" t="n">
-        <v>16.32374</v>
+        <v>16.41525</v>
       </c>
       <c r="E20" t="n">
-        <v>16.64138</v>
+        <v>16.73903</v>
       </c>
       <c r="F20" t="n">
-        <v>55.99916</v>
+        <v>42.44682</v>
       </c>
       <c r="G20" t="n">
-        <v>41.47616</v>
+        <v>0.04968</v>
       </c>
       <c r="H20" t="n">
-        <v>85.74816</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.05031</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.78614</v>
+        <v>1.76223</v>
       </c>
     </row>
     <row r="21">
@@ -1086,12 +958,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -1103,23 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.69092</v>
+        <v>15.66087</v>
       </c>
       <c r="D22" t="n">
-        <v>15.88842</v>
+        <v>15.31119</v>
       </c>
       <c r="E22" t="n">
-        <v>16.36186</v>
+        <v>15.60383</v>
       </c>
       <c r="F22" t="n">
-        <v>21.61127</v>
-      </c>
-      <c r="G22" t="n">
-        <v>34.3953</v>
+        <v>248.87491</v>
       </c>
     </row>
     <row r="23">
@@ -1129,19 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.44956</v>
+        <v>15.82301</v>
       </c>
       <c r="D23" t="n">
-        <v>16.21583</v>
+        <v>15.6049</v>
       </c>
       <c r="E23" t="n">
-        <v>16.55682</v>
+        <v>15.80389</v>
       </c>
       <c r="F23" t="n">
-        <v>21.59009</v>
-      </c>
-      <c r="G23" t="n">
-        <v>33.99727</v>
+        <v>252.90617</v>
       </c>
     </row>
     <row r="24">
@@ -1151,19 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.56614</v>
+        <v>15.82875</v>
       </c>
       <c r="D24" t="n">
-        <v>15.92252</v>
+        <v>15.37667</v>
       </c>
       <c r="E24" t="n">
-        <v>16.1724</v>
+        <v>15.66161</v>
       </c>
       <c r="F24" t="n">
-        <v>21.5949</v>
-      </c>
-      <c r="G24" t="n">
-        <v>34.23874</v>
+        <v>253.25254</v>
       </c>
     </row>
     <row r="25">
@@ -1173,19 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.35573</v>
+        <v>15.7166</v>
       </c>
       <c r="D25" t="n">
-        <v>15.99694</v>
+        <v>15.10471</v>
       </c>
       <c r="E25" t="n">
-        <v>16.66419</v>
+        <v>15.6089</v>
       </c>
       <c r="F25" t="n">
-        <v>21.75978</v>
-      </c>
-      <c r="G25" t="n">
-        <v>33.14304</v>
+        <v>254.48322</v>
       </c>
     </row>
     <row r="26">
@@ -1195,19 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.57749</v>
+        <v>15.64893</v>
       </c>
       <c r="D26" t="n">
-        <v>16.2613</v>
+        <v>15.3415</v>
       </c>
       <c r="E26" t="n">
-        <v>16.47121</v>
+        <v>15.54968</v>
       </c>
       <c r="F26" t="n">
-        <v>21.91867</v>
-      </c>
-      <c r="G26" t="n">
-        <v>34.28978</v>
+        <v>253.66507</v>
       </c>
     </row>
     <row r="27">
@@ -1217,19 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.57738</v>
+        <v>15.6472</v>
       </c>
       <c r="D27" t="n">
-        <v>15.87537</v>
+        <v>15.43814</v>
       </c>
       <c r="E27" t="n">
-        <v>16.0433</v>
+        <v>15.56171</v>
       </c>
       <c r="F27" t="n">
-        <v>21.58939</v>
-      </c>
-      <c r="G27" t="n">
-        <v>33.94216</v>
+        <v>248.38159</v>
       </c>
     </row>
     <row r="28">
@@ -1239,19 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.63961</v>
+        <v>15.75892</v>
       </c>
       <c r="D28" t="n">
-        <v>16.11077</v>
+        <v>15.36323</v>
       </c>
       <c r="E28" t="n">
-        <v>16.17387</v>
+        <v>15.55356</v>
       </c>
       <c r="F28" t="n">
-        <v>21.36648</v>
-      </c>
-      <c r="G28" t="n">
-        <v>33.91562</v>
+        <v>256.85315</v>
       </c>
     </row>
     <row r="29">
@@ -1261,19 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.35077</v>
+        <v>15.59115</v>
       </c>
       <c r="D29" t="n">
-        <v>15.77686</v>
+        <v>15.50846</v>
       </c>
       <c r="E29" t="n">
-        <v>16.23808</v>
+        <v>15.5844</v>
       </c>
       <c r="F29" t="n">
-        <v>21.72796</v>
-      </c>
-      <c r="G29" t="n">
-        <v>33.85949</v>
+        <v>251.07254</v>
       </c>
     </row>
     <row r="30">
@@ -1283,19 +1126,744 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.71738</v>
+        <v>15.57173</v>
       </c>
       <c r="D30" t="n">
-        <v>16.24382</v>
+        <v>15.32805</v>
       </c>
       <c r="E30" t="n">
-        <v>16.37872</v>
+        <v>15.43997</v>
       </c>
       <c r="F30" t="n">
-        <v>21.8544</v>
-      </c>
-      <c r="G30" t="n">
-        <v>33.60987</v>
+        <v>257.12653</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.57033</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.08387</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.33423</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.81628</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.28837</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.77109</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.05266</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.6267</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.95808</v>
+      </c>
+      <c r="G33" t="n">
+        <v>33.16201</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.69135</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15.56414</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.37462</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.4733</v>
+      </c>
+      <c r="G34" t="n">
+        <v>33.6481</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.75186</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15.49934</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.64953</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22.01202</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34.1203</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.36353</v>
+      </c>
+      <c r="D36" t="n">
+        <v>15.63143</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.00293</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.79333</v>
+      </c>
+      <c r="G36" t="n">
+        <v>33.67642</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.60762</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.6282</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.3294</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.99094</v>
+      </c>
+      <c r="G37" t="n">
+        <v>33.96049</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.70303</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15.71413</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.60456</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.61985</v>
+      </c>
+      <c r="G38" t="n">
+        <v>33.71611</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.83015</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.1944</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.27033</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.64254</v>
+      </c>
+      <c r="G39" t="n">
+        <v>33.38398</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.74658</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.83587</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.56304</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.60205</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.04477</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.80073</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.68993</v>
+      </c>
+      <c r="E42" t="n">
+        <v>15.88491</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.9422</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.18609</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.7809</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.99926</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.44155</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.35362</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.60149</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.70065</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.06324</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.08332</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.39209</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.38163</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.82526</v>
+      </c>
+      <c r="D45" t="n">
+        <v>15.99245</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.13165</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.64962</v>
+      </c>
+      <c r="G45" t="n">
+        <v>33.77133</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.25313</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.83458</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.18572</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.79148</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.11324</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.70826</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.0557</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.05638</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.61003</v>
+      </c>
+      <c r="G47" t="n">
+        <v>33.73929</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.78651</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.00961</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.17344</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.74705</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.0414</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.73568</v>
+      </c>
+      <c r="D49" t="n">
+        <v>15.9472</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.27113</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.50337</v>
+      </c>
+      <c r="G49" t="n">
+        <v>33.37336</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.62264</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.01216</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.10173</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.43281</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.13069</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.60125</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.09596</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.61049</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.1216</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.61092</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.10859</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.5968599999999999</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.08669</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6086</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.11636</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.60079</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.09729</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.61787</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.08269</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.60656</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.09849</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.60965</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.10929</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.61417</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.1196</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.59742</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.07961</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.60515</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.14079</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.59841</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.10192</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.59108</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.11517</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.6027</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.10617</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.61141</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.08562</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.60243</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.09946</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.5891</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.11234</v>
       </c>
     </row>
   </sheetData>
